--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T12:57:47+00:00</t>
+    <t>2026-02-10T07:06:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T07:06:10+00:00</t>
+    <t>2026-02-10T09:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T09:12:19+00:00</t>
+    <t>2026-02-10T11:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T11:08:27+00:00</t>
+    <t>2026-02-10T14:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T14:07:12+00:00</t>
+    <t>2026-02-10T15:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T15:59:15+00:00</t>
+    <t>2026-02-12T14:06:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:06:59+00:00</t>
+    <t>2026-02-13T17:10:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T17:10:39+00:00</t>
+    <t>2026-02-18T15:13:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T15:13:02+00:00</t>
+    <t>2026-02-18T16:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T16:58:33+00:00</t>
+    <t>2026-02-19T09:33:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
